--- a/data/trans_orig/IP07C03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C03-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32293</t>
+          <t>32463</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31309</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44670</t>
+          <t>44236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54597</t>
+          <t>54234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72753</t>
+          <t>72655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,91%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22571</t>
+          <t>21845</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>35006</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33172</t>
+          <t>34011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>46732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64486</t>
+          <t>65356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>52,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47660</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63463</t>
+          <t>63203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41026</t>
+          <t>42600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56991</t>
+          <t>57018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94212</t>
+          <t>95652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116023</t>
+          <t>117335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>61,34%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31663</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47027</t>
+          <t>46965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>27985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42566</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64371</t>
+          <t>62886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85744</t>
+          <t>84009</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>14455</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37584</t>
+          <t>37249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>22567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52402</t>
+          <t>51694</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68399</t>
+          <t>68294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23775</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35884</t>
+          <t>35796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41898</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58600</t>
+          <t>59649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28716</t>
+          <t>28834</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35053</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49713</t>
+          <t>49329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68482</t>
+          <t>68483</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89463</t>
+          <t>89171</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40342</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34858</t>
+          <t>34885</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49586</t>
+          <t>49576</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63067</t>
+          <t>63697</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83988</t>
+          <t>84363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,69%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>136044</t>
+          <t>134971</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>163485</t>
+          <t>162810</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>144211</t>
+          <t>144813</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>172413</t>
+          <t>172218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>288252</t>
+          <t>289017</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>326861</t>
+          <t>327604</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107415</t>
+          <t>107607</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>132846</t>
+          <t>134436</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>119161</t>
+          <t>120443</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>148132</t>
+          <t>148098</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>235800</t>
+          <t>235121</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>273946</t>
+          <t>274062</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22027</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38783</t>
+          <t>38337</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36311</t>
+          <t>36167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41666</t>
+          <t>41288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60364</t>
+          <t>60315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44340</t>
+          <t>43520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33187</t>
+          <t>33540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48003</t>
+          <t>46694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67335</t>
+          <t>68362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87042</t>
+          <t>88110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32169</t>
+          <t>31582</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47978</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37078</t>
+          <t>36831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52486</t>
+          <t>52244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>74102</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95490</t>
+          <t>95776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44586</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60281</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37643</t>
+          <t>37706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53396</t>
+          <t>52917</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87724</t>
+          <t>87382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108644</t>
+          <t>108966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,46%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>14342</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>17559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31521</t>
+          <t>31499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44580</t>
+          <t>44500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52895</t>
+          <t>52967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70993</t>
+          <t>70685</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31428</t>
+          <t>30491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44515</t>
+          <t>43510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19102</t>
+          <t>19024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31711</t>
+          <t>31794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53600</t>
+          <t>52864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71161</t>
+          <t>71228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>431</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33716</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30505</t>
+          <t>30582</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47040</t>
+          <t>46669</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53597</t>
+          <t>54337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75863</t>
+          <t>76375</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45672</t>
+          <t>45908</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60543</t>
+          <t>60753</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37130</t>
+          <t>36810</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53365</t>
+          <t>53085</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87123</t>
+          <t>87027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>109431</t>
+          <t>109867</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>98087</t>
+          <t>97841</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>124966</t>
+          <t>124482</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135170</t>
+          <t>135433</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>165059</t>
+          <t>163032</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>240732</t>
+          <t>242737</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>284972</t>
+          <t>283460</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>165690</t>
+          <t>166414</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>194474</t>
+          <t>194426</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>141861</t>
+          <t>143213</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>170151</t>
+          <t>171316</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>314991</t>
+          <t>316568</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>358204</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22352</t>
+          <t>22909</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>21048</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>28432</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41398</t>
+          <t>41387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>31303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45824</t>
+          <t>45791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63604</t>
+          <t>63560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84680</t>
+          <t>83809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>23285</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36939</t>
+          <t>36627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35384</t>
+          <t>35951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48840</t>
+          <t>49086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69015</t>
+          <t>68435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,87%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39944</t>
+          <t>41169</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57151</t>
+          <t>56385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51099</t>
+          <t>51971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68345</t>
+          <t>67909</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98203</t>
+          <t>97237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120479</t>
+          <t>120527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37904</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53506</t>
+          <t>53920</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27625</t>
+          <t>27878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43453</t>
+          <t>42611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69820</t>
+          <t>69609</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92232</t>
+          <t>92514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12606</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,47 +8974,47 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>12,15%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>13230</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>7918</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>19363</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>13230</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>8466</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>19925</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>33385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47302</t>
+          <t>46689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>40193</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54154</t>
+          <t>53775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77497</t>
+          <t>77918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97257</t>
+          <t>96400</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>31718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17935</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31569</t>
+          <t>32054</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41461</t>
+          <t>41979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60463</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42325</t>
+          <t>42505</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60608</t>
+          <t>59410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39459</t>
+          <t>39154</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56229</t>
+          <t>56743</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86109</t>
+          <t>86886</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34288</t>
+          <t>35796</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52709</t>
+          <t>53058</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36504</t>
+          <t>36561</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53154</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>76219</t>
+          <t>76410</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101688</t>
+          <t>99908</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>20376</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>160790</t>
+          <t>160778</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>190672</t>
+          <t>191182</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>178840</t>
+          <t>179384</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208334</t>
+          <t>209728</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>350503</t>
+          <t>348197</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>393340</t>
+          <t>392057</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>128979</t>
+          <t>130300</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>159386</t>
+          <t>161745</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>119224</t>
+          <t>118549</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>149101</t>
+          <t>147671</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>257244</t>
+          <t>256623</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>299951</t>
+          <t>299379</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28004</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49594</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,47 +11133,47 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>6162</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>6162</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>2910</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>11248</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
